--- a/results/breakdown/2020/nitrous oxide production, AON 100, fossil ammonia.xlsx
+++ b/results/breakdown/2020/nitrous oxide production, AON 100, fossil ammonia.xlsx
@@ -426,7 +426,7 @@
         <v>4</v>
       </c>
       <c r="D2">
-        <v>2.821191691143676</v>
+        <v>2.821191691143675</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -460,7 +460,7 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>0.0005793451294999568</v>
+        <v>0.0005793451294999553</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -477,7 +477,7 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>0.03412314645233022</v>
+        <v>0.03412314645233021</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -494,7 +494,7 @@
         <v>8</v>
       </c>
       <c r="D6">
-        <v>0.001696936407882483</v>
+        <v>0.001696936407882484</v>
       </c>
       <c r="E6">
         <v>1</v>

--- a/results/breakdown/2020/nitrous oxide production, AON 100, fossil ammonia.xlsx
+++ b/results/breakdown/2020/nitrous oxide production, AON 100, fossil ammonia.xlsx
@@ -426,7 +426,7 @@
         <v>4</v>
       </c>
       <c r="D2">
-        <v>2.821191691143675</v>
+        <v>2.821191896547139</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -443,7 +443,7 @@
         <v>5</v>
       </c>
       <c r="D3">
-        <v>2.78479232169343</v>
+        <v>2.784792369255294</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -460,7 +460,7 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>0.0005793451294999553</v>
+        <v>0.0005793451467072054</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -477,7 +477,7 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>0.03412314645233021</v>
+        <v>0.03412314779521224</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -494,7 +494,7 @@
         <v>8</v>
       </c>
       <c r="D6">
-        <v>0.001696936407882484</v>
+        <v>0.001696936436860225</v>
       </c>
       <c r="E6">
         <v>1</v>

--- a/results/breakdown/2020/nitrous oxide production, AON 100, fossil ammonia.xlsx
+++ b/results/breakdown/2020/nitrous oxide production, AON 100, fossil ammonia.xlsx
@@ -460,7 +460,7 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>0.0005793451467072054</v>
+        <v>0.0005793451467072008</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -494,7 +494,7 @@
         <v>8</v>
       </c>
       <c r="D6">
-        <v>0.001696936436860225</v>
+        <v>0.001696936436860226</v>
       </c>
       <c r="E6">
         <v>1</v>
